--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.76481043727402</v>
+        <v>8.736781696057029</v>
       </c>
       <c r="D2" t="n">
-        <v>53.46068196153624</v>
+        <v>8.687360818749639</v>
       </c>
       <c r="E2" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F2" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.75614629796728</v>
+        <v>6.460373773419684</v>
       </c>
       <c r="D3" t="n">
-        <v>39.35032617320056</v>
+        <v>6.394428003145091</v>
       </c>
       <c r="E3" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.96554335956557</v>
+        <v>8.281900795929404</v>
       </c>
       <c r="D4" t="n">
-        <v>50.76172352430072</v>
+        <v>8.248780072698867</v>
       </c>
       <c r="E4" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F4" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.88887468093011</v>
+        <v>7.619442135651143</v>
       </c>
       <c r="D5" t="n">
-        <v>46.37079758561777</v>
+        <v>7.535254607662888</v>
       </c>
       <c r="E5" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.39830110162256</v>
+        <v>8.839723929013665</v>
       </c>
       <c r="D6" t="n">
-        <v>53.92918864220623</v>
+        <v>8.763493154358514</v>
       </c>
       <c r="E6" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F6" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.60591692052441</v>
+        <v>6.760961499585218</v>
       </c>
       <c r="D7" t="n">
-        <v>41.01056747970814</v>
+        <v>6.664217215452574</v>
       </c>
       <c r="E7" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F7" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.49730824805597</v>
+        <v>9.668312590309094</v>
       </c>
       <c r="D8" t="n">
-        <v>59.0885378577353</v>
+        <v>9.601887401881987</v>
       </c>
       <c r="E8" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F8" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.19864526931376</v>
+        <v>3.769779856263486</v>
       </c>
       <c r="D9" t="n">
-        <v>22.83108319084683</v>
+        <v>3.71005101851261</v>
       </c>
       <c r="E9" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F9" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.99409158434401</v>
+        <v>4.061539882455901</v>
       </c>
       <c r="D10" t="n">
-        <v>24.94558781827763</v>
+        <v>4.053658020470115</v>
       </c>
       <c r="E10" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F10" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4.204857005014601</v>
+        <v>0.6832892633148726</v>
       </c>
       <c r="D11" t="n">
-        <v>4.770832463691972</v>
+        <v>0.7752602753499456</v>
       </c>
       <c r="E11" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F11" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65967881660853</v>
+        <v>3.032197807698886</v>
       </c>
       <c r="D12" t="n">
-        <v>19.3139411150796</v>
+        <v>3.138515431200435</v>
       </c>
       <c r="E12" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F12" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.08803593033014</v>
+        <v>3.589305838678647</v>
       </c>
       <c r="D13" t="n">
-        <v>22.66267315864224</v>
+        <v>3.682684388279364</v>
       </c>
       <c r="E13" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F13" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.55045015458438</v>
+        <v>5.776948150119963</v>
       </c>
       <c r="D14" t="n">
-        <v>31.52199483475546</v>
+        <v>5.122324160647763</v>
       </c>
       <c r="E14" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F14" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.96567529220393</v>
+        <v>6.169422234983138</v>
       </c>
       <c r="D15" t="n">
-        <v>25.41790979686199</v>
+        <v>4.130410341990074</v>
       </c>
       <c r="E15" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F15" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.21668996805516</v>
+        <v>6.535212119808964</v>
       </c>
       <c r="D16" t="n">
-        <v>26.30151061559469</v>
+        <v>4.273995475034138</v>
       </c>
       <c r="E16" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F16" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.57601233986862</v>
+        <v>5.781102005228651</v>
       </c>
       <c r="D17" t="n">
-        <v>35.42396120058593</v>
+        <v>5.756393695095213</v>
       </c>
       <c r="E17" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F17" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.5549188130212</v>
+        <v>8.702674307115945</v>
       </c>
       <c r="D18" t="n">
-        <v>51.75212207801333</v>
+        <v>8.409719837677166</v>
       </c>
       <c r="E18" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F18" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>17.96689590257104</v>
+        <v>2.919620584167793</v>
       </c>
       <c r="D19" t="n">
-        <v>12.41348670616744</v>
+        <v>2.017191589752209</v>
       </c>
       <c r="E19" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F19" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>44.5200501632501</v>
+        <v>7.234508151528141</v>
       </c>
       <c r="D20" t="n">
-        <v>30.52961285624237</v>
+        <v>4.961062089139386</v>
       </c>
       <c r="E20" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F20" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>24.89031289769729</v>
+        <v>4.044675845875809</v>
       </c>
       <c r="D21" t="n">
-        <v>18.41117957972786</v>
+        <v>2.991816681705777</v>
       </c>
       <c r="E21" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F21" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>52.08842720660163</v>
+        <v>8.464369421072766</v>
       </c>
       <c r="D22" t="n">
-        <v>42.44413421047737</v>
+        <v>6.897171809202572</v>
       </c>
       <c r="E22" t="n">
-        <v>14.57595184866638</v>
+        <v>2.368592175408286</v>
       </c>
       <c r="F22" t="n">
-        <v>14.75330469670135</v>
+        <v>2.39741201321397</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
